--- a/src/test-data/data for sign-up chat.xlsx
+++ b/src/test-data/data for sign-up chat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Gyansetu\G_TestCase001\src\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1BFBA2-24D8-4D1B-8847-C29D38920749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC135475-5B51-4F1A-B9F2-E51986E94DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SchoolUser_Registration" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="261">
   <si>
     <t>Email ID</t>
   </si>
@@ -471,15 +471,9 @@
     <t>Vincent JJ</t>
   </si>
   <si>
-    <t>shanmukanct66@yopmail.com</t>
-  </si>
-  <si>
     <t>Sharan Ji</t>
   </si>
   <si>
-    <t>nazeera122@yopmail.com</t>
-  </si>
-  <si>
     <t>Ansi N</t>
   </si>
   <si>
@@ -681,9 +675,6 @@
     <t>trunneucauxapei-9464@yopmail.com</t>
   </si>
   <si>
-    <t>Adam V</t>
-  </si>
-  <si>
     <t>Jo V</t>
   </si>
   <si>
@@ -768,21 +759,6 @@
     <t>dmmkioi899@yopmail.com</t>
   </si>
   <si>
-    <t>AERONAUTICAL ENGINEERING</t>
-  </si>
-  <si>
-    <t>Semester 4</t>
-  </si>
-  <si>
-    <t>Lab 4</t>
-  </si>
-  <si>
-    <t>Soman SS</t>
-  </si>
-  <si>
-    <t>ziloikuteco-2589@yopmail.com</t>
-  </si>
-  <si>
     <t>Velammal University</t>
   </si>
   <si>
@@ -798,13 +774,55 @@
     <t>gepihemeuteu-1849@yopmail.com</t>
   </si>
   <si>
-    <t>Sintthu N</t>
-  </si>
-  <si>
     <t>sinthuyy888@yopmail.com</t>
   </si>
   <si>
-    <t>Anagha CK</t>
+    <t>sanalvava89@yopmail.com</t>
+  </si>
+  <si>
+    <t>ENGINEERING Mechanical Lab</t>
+  </si>
+  <si>
+    <t>neethanee677@yopmail.com</t>
+  </si>
+  <si>
+    <t>frafollufrullou-6852@yopmail.com</t>
+  </si>
+  <si>
+    <t>ELECTRICAL AND ELECTRONICS ENGINEERING</t>
+  </si>
+  <si>
+    <t>veronica867@yopmail.com</t>
+  </si>
+  <si>
+    <t>Nttva V</t>
+  </si>
+  <si>
+    <t>neeharaaa788@yopmail.com</t>
+  </si>
+  <si>
+    <t>repltte67@yopmail.com</t>
+  </si>
+  <si>
+    <t>walnutyy55@yopmail.com</t>
+  </si>
+  <si>
+    <t>himha66@yopmail.com</t>
+  </si>
+  <si>
+    <t>Manimal HSS</t>
+  </si>
+  <si>
+    <t>English First</t>
+  </si>
+  <si>
+    <t>Sanju Vava</t>
+  </si>
+  <si>
+    <t>Rep N</t>
+  </si>
+  <si>
+    <t>Studying</t>
   </si>
 </sst>
 </file>
@@ -1932,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3FCDD0-35E5-40DE-9EAB-7DC01EE1849E}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.44140625" bestFit="1" customWidth="1"/>
@@ -1953,10 +1971,10 @@
     </row>
     <row r="2" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A2" s="22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B2" s="23">
-        <v>8886663015</v>
+        <v>8886663019</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>3</v>
@@ -1964,26 +1982,32 @@
     </row>
     <row r="3" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A3" s="22" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B3" s="23">
-        <v>8886663010</v>
+        <v>8886663018</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="19" customFormat="1" ht="15.6">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
+      <c r="A4" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="23">
+        <v>8886663017</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A5" s="22" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="B5" s="23">
-        <v>8886663009</v>
+        <v>8886663015</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>3</v>
@@ -1991,10 +2015,10 @@
     </row>
     <row r="6" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A6" s="22" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B6" s="23">
-        <v>8886663008</v>
+        <v>8886663010</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>3</v>
@@ -2002,10 +2026,10 @@
     </row>
     <row r="7" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A7" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B7" s="23">
-        <v>8886663007</v>
+        <v>8886663009</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>3</v>
@@ -2013,24 +2037,36 @@
     </row>
     <row r="8" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A8" s="22" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="B8" s="23">
-        <v>8886663006</v>
+        <v>8886663008</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="19" customFormat="1" ht="15.6">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="23">
+        <v>8886663007</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:3" s="19" customFormat="1" ht="15.6">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="23">
+        <v>8886663006</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A11" s="22"/>
@@ -2132,13 +2168,13 @@
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="1:3" ht="15.6">
-      <c r="A31" s="23"/>
+    <row r="31" spans="1:3" s="19" customFormat="1" ht="15.6">
+      <c r="A31" s="22"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
     </row>
-    <row r="32" spans="1:3" ht="15.6">
-      <c r="A32" s="23"/>
+    <row r="32" spans="1:3" s="19" customFormat="1" ht="15.6">
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
     </row>
@@ -2176,6 +2212,16 @@
       <c r="A39" s="23"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
+    </row>
+    <row r="40" spans="1:3" ht="15.6">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+    </row>
+    <row r="41" spans="1:3" ht="15.6">
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2308,7 +2354,7 @@
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" ht="28.8">
       <c r="A2" s="12" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B2" s="12">
         <v>26</v>
@@ -2341,7 +2387,7 @@
         <v>35</v>
       </c>
       <c r="L2" s="29" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>13</v>
@@ -2350,7 +2396,7 @@
         <v>123</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>116</v>
+        <v>260</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>118</v>
@@ -2359,7 +2405,7 @@
         <v>9876655555</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S2" s="12" t="s">
         <v>41</v>
@@ -2368,13 +2414,13 @@
         <v>55</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="W2" s="2">
-        <v>8876655480</v>
+        <v>8876655466</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>42</v>
@@ -2400,7 +2446,7 @@
     </row>
     <row r="3" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A3" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B3" s="12">
         <v>26</v>
@@ -2451,7 +2497,7 @@
         <v>9876655555</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>41</v>
@@ -2463,7 +2509,7 @@
         <v>72</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="W3" s="2">
         <v>8876655480</v>
@@ -2492,7 +2538,7 @@
     </row>
     <row r="4" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A4" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B4" s="12">
         <v>26</v>
@@ -2525,7 +2571,7 @@
         <v>35</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>13</v>
@@ -2543,7 +2589,7 @@
         <v>9876655555</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S4" s="12" t="s">
         <v>41</v>
@@ -2552,10 +2598,10 @@
         <v>55</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="W4" s="2">
         <v>8876655012</v>
@@ -2584,7 +2630,7 @@
     </row>
     <row r="5" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A5" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" s="12">
         <v>26</v>
@@ -2617,7 +2663,7 @@
         <v>35</v>
       </c>
       <c r="L5" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M5" s="12" t="s">
         <v>13</v>
@@ -2635,7 +2681,7 @@
         <v>9876655555</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>41</v>
@@ -2644,10 +2690,10 @@
         <v>55</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W5" s="2">
         <v>8876655011</v>
@@ -2676,7 +2722,7 @@
     </row>
     <row r="6" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A6" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B6" s="12">
         <v>26</v>
@@ -2709,7 +2755,7 @@
         <v>35</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>13</v>
@@ -2727,7 +2773,7 @@
         <v>9876655555</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>41</v>
@@ -2736,10 +2782,10 @@
         <v>55</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W6" s="2">
         <v>8876655011</v>
@@ -2768,7 +2814,7 @@
     </row>
     <row r="7" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A7" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B7" s="12">
         <v>26</v>
@@ -2801,7 +2847,7 @@
         <v>35</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>13</v>
@@ -2819,7 +2865,7 @@
         <v>9876655555</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>41</v>
@@ -2828,10 +2874,10 @@
         <v>55</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="W7" s="2">
         <v>8876655011</v>
@@ -2860,7 +2906,7 @@
     </row>
     <row r="8" spans="1:31" s="1" customFormat="1" ht="31.2">
       <c r="A8" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B8" s="12">
         <v>26</v>
@@ -2893,7 +2939,7 @@
         <v>35</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>13</v>
@@ -2911,7 +2957,7 @@
         <v>9876655555</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>41</v>
@@ -2920,10 +2966,10 @@
         <v>55</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="W8" s="2">
         <v>8876655011</v>
@@ -2952,7 +2998,7 @@
     </row>
     <row r="9" spans="1:31" s="1" customFormat="1" ht="28.8">
       <c r="A9" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B9" s="12">
         <v>26</v>
@@ -3015,7 +3061,7 @@
         <v>98</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="W9" s="2">
         <v>8876655555</v>
@@ -3044,7 +3090,7 @@
     </row>
     <row r="10" spans="1:31" s="1" customFormat="1" ht="28.8">
       <c r="A10" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" s="12">
         <v>26</v>
@@ -3106,8 +3152,8 @@
       <c r="U10" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="V10" t="s">
-        <v>143</v>
+      <c r="V10" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="W10" s="12">
         <v>7564531233</v>
@@ -3198,8 +3244,8 @@
       <c r="U11" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="V11" s="17" t="s">
-        <v>109</v>
+      <c r="V11" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="W11" s="12">
         <v>5345643555</v>
@@ -3699,7 +3745,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C8DD64-AF8B-4BA8-8DA4-5733BD431885}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="50.88671875" bestFit="1" customWidth="1"/>
@@ -3719,112 +3765,130 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6">
-      <c r="A2" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="23">
-        <v>8886663057</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>181</v>
-      </c>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" ht="15.6">
       <c r="A3" s="16" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="B3" s="23">
-        <v>8886663056</v>
+        <v>8886663063</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6">
       <c r="A4" s="16" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="B4" s="23">
-        <v>8886663055</v>
+        <v>8886663059</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6">
       <c r="A5" s="16" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="B5" s="23">
-        <v>8886663054</v>
+        <v>8886663058</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6">
       <c r="A6" s="16" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B6" s="23">
-        <v>8886663098</v>
+        <v>8886663057</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6">
       <c r="A7" s="16" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B7" s="23">
-        <v>8886663035</v>
+        <v>8886663056</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6">
       <c r="A8" s="16" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B8" s="23">
-        <v>8886663034</v>
+        <v>8886663055</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6">
       <c r="A9" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="23">
+        <v>8886663054</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.6">
+      <c r="A10" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="23">
+        <v>8886663098</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6">
+      <c r="A11" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B11" s="23">
+        <v>8886663035</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.6">
+      <c r="A12" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="23">
+        <v>8886663034</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6">
+      <c r="A13" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="23">
         <v>8886663033</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6">
-      <c r="A10" s="16"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-    </row>
-    <row r="11" spans="1:3" ht="15.6">
-      <c r="A11" s="16"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-    </row>
-    <row r="12" spans="1:3" ht="15.6">
-      <c r="A12" s="16"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.6">
-      <c r="A13" s="16"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="C13" s="23" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="14" spans="1:3" ht="15.6">
       <c r="A14" s="16"/>
@@ -3867,6 +3931,7 @@
       <c r="C21" s="23"/>
     </row>
     <row r="22" spans="1:3" ht="15.6">
+      <c r="A22" s="16"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
     </row>
@@ -3886,30 +3951,33 @@
       <c r="C25" s="23"/>
     </row>
     <row r="26" spans="1:3" ht="15.6">
-      <c r="A26" s="22"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
     </row>
     <row r="27" spans="1:3" ht="15.6">
       <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
     </row>
     <row r="28" spans="1:3" ht="15.6">
       <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
     </row>
     <row r="29" spans="1:3" ht="15.6">
       <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-    </row>
-    <row r="30" spans="1:3" ht="21.6">
-      <c r="A30" s="34"/>
-      <c r="B30" s="16"/>
-    </row>
-    <row r="31" spans="1:3" ht="18">
-      <c r="A31" s="35"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+    </row>
+    <row r="30" spans="1:3" ht="15.6">
+      <c r="A30" s="22"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+    </row>
+    <row r="31" spans="1:3" ht="15.6">
+      <c r="A31" s="16"/>
       <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" ht="15.6">
       <c r="A32" s="16"/>
@@ -3919,27 +3987,43 @@
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
     </row>
-    <row r="34" spans="1:10" ht="15.6">
-      <c r="A34" s="16"/>
+    <row r="34" spans="1:10" ht="21.6">
+      <c r="A34" s="34"/>
       <c r="B34" s="16"/>
     </row>
-    <row r="35" spans="1:10" ht="15.6">
-      <c r="A35" s="36"/>
+    <row r="35" spans="1:10" ht="18">
+      <c r="A35" s="35"/>
+      <c r="B35" s="16"/>
     </row>
     <row r="36" spans="1:10" ht="15.6">
-      <c r="A36" s="36"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
     </row>
     <row r="37" spans="1:10" ht="15.6">
-      <c r="A37" s="36"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
     </row>
     <row r="38" spans="1:10" ht="15.6">
-      <c r="A38" s="36"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
     </row>
     <row r="39" spans="1:10" ht="15.6">
       <c r="A39" s="36"/>
     </row>
+    <row r="40" spans="1:10" ht="15.6">
+      <c r="A40" s="36"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.6">
+      <c r="A41" s="36"/>
+    </row>
     <row r="42" spans="1:10" ht="15.6">
-      <c r="J42" s="16"/>
+      <c r="A42" s="36"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.6">
+      <c r="A43" s="36"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.6">
+      <c r="J46" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -3969,7 +4053,7 @@
     <col min="22" max="22" width="4" style="8" customWidth="1"/>
     <col min="23" max="23" width="11.77734375" style="8" customWidth="1"/>
     <col min="24" max="24" width="20.77734375" style="2" customWidth="1"/>
-    <col min="25" max="25" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
@@ -4073,13 +4157,13 @@
     </row>
     <row r="2" spans="1:33" ht="96">
       <c r="A2" s="5" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="B2" s="5">
         <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D2" s="5">
         <v>2000</v>
@@ -4106,16 +4190,16 @@
         <v>49</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="P2" s="11">
         <v>2024</v>
@@ -4130,20 +4214,20 @@
         <v>9876655555</v>
       </c>
       <c r="T2" s="37" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Y2" s="2">
-        <v>9865444444</v>
+        <v>8876655901</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>42</v>
@@ -4161,22 +4245,22 @@
         <v>788764</v>
       </c>
       <c r="AE2" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG2" s="31"/>
     </row>
     <row r="3" spans="1:33" ht="96">
       <c r="A3" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B3" s="5">
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D3" s="5">
         <v>2000</v>
@@ -4206,10 +4290,10 @@
         <v>100</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>56</v>
@@ -4227,17 +4311,17 @@
         <v>9876655555</v>
       </c>
       <c r="T3" s="37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y3" s="2">
         <v>8876655919</v>
@@ -4258,16 +4342,16 @@
         <v>788764</v>
       </c>
       <c r="AE3" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG3" s="31"/>
     </row>
     <row r="4" spans="1:33" ht="96">
       <c r="A4" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B4" s="5">
         <v>26</v>
@@ -4303,7 +4387,7 @@
         <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>73</v>
@@ -4324,17 +4408,17 @@
         <v>9876655555</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y4" s="2">
         <v>8876655901</v>
@@ -4355,16 +4439,16 @@
         <v>788764</v>
       </c>
       <c r="AE4" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG4" s="31"/>
     </row>
     <row r="5" spans="1:33" ht="96">
       <c r="A5" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="5">
         <v>26</v>
@@ -4400,7 +4484,7 @@
         <v>50</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>73</v>
@@ -4421,17 +4505,17 @@
         <v>9876655555</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="Y5" s="2">
         <v>8876655901</v>
@@ -4452,16 +4536,16 @@
         <v>788764</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG5" s="31"/>
     </row>
     <row r="6" spans="1:33" ht="96">
       <c r="A6" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B6" s="5">
         <v>26</v>
@@ -4497,7 +4581,7 @@
         <v>50</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>73</v>
@@ -4518,17 +4602,17 @@
         <v>9876655555</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Y6" s="2">
         <v>8876655000</v>
@@ -4549,16 +4633,16 @@
         <v>788764</v>
       </c>
       <c r="AE6" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG6" s="31"/>
     </row>
     <row r="7" spans="1:33" ht="96">
       <c r="A7" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B7" s="5">
         <v>26</v>
@@ -4594,7 +4678,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>73</v>
@@ -4615,17 +4699,17 @@
         <v>9876655555</v>
       </c>
       <c r="T7" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Y7" s="2">
         <v>8876655578</v>
@@ -4646,16 +4730,16 @@
         <v>788764</v>
       </c>
       <c r="AE7" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG7" s="31"/>
     </row>
     <row r="8" spans="1:33" ht="96">
       <c r="A8" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B8" s="5">
         <v>26</v>
@@ -4691,7 +4775,7 @@
         <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>73</v>
@@ -4712,17 +4796,17 @@
         <v>9876655555</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y8" s="2">
         <v>8876655453</v>
@@ -4743,16 +4827,16 @@
         <v>788764</v>
       </c>
       <c r="AE8" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG8" s="31"/>
     </row>
     <row r="9" spans="1:33" ht="96">
       <c r="A9" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B9" s="5">
         <v>26</v>
@@ -4788,7 +4872,7 @@
         <v>50</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>73</v>
@@ -4809,17 +4893,17 @@
         <v>9876655555</v>
       </c>
       <c r="T9" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y9" s="2">
         <v>8876655511</v>
@@ -4840,16 +4924,16 @@
         <v>788764</v>
       </c>
       <c r="AE9" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG9" s="31"/>
     </row>
     <row r="10" spans="1:33" ht="96">
       <c r="A10" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B10" s="5">
         <v>26</v>
@@ -4885,7 +4969,7 @@
         <v>50</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>59</v>
@@ -4906,17 +4990,17 @@
         <v>9876655555</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>58</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y10" s="2">
         <v>8876655511</v>
@@ -4937,16 +5021,16 @@
         <v>788764</v>
       </c>
       <c r="AE10" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG10" s="31"/>
     </row>
     <row r="11" spans="1:33" ht="96">
       <c r="A11" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" s="5">
         <v>26</v>
@@ -5015,7 +5099,7 @@
         <v>104</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Y11" s="5">
         <v>9998864431</v>
@@ -5383,10 +5467,10 @@
   <sheetData>
     <row r="1" spans="1:15" ht="31.2">
       <c r="A1" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>29</v>
@@ -5398,13 +5482,13 @@
         <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I1" s="33" t="s">
         <v>51</v>
@@ -5419,27 +5503,27 @@
         <v>54</v>
       </c>
       <c r="M1" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="O1" s="33" t="s">
         <v>159</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="17" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="17">
         <v>23</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E2" s="17">
         <v>1993</v>
@@ -5448,16 +5532,16 @@
         <v>9998881155</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N2" s="17" t="s">
         <v>97</v>
@@ -5468,16 +5552,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C3" s="17">
         <v>22</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E3" s="17">
         <v>2000</v>
@@ -5486,7 +5570,7 @@
         <v>9998881139</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>49</v>
@@ -5495,33 +5579,33 @@
         <v>100</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K3" s="17">
         <v>1</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>97</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="17" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C4" s="17">
         <v>22</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E4" s="17">
         <v>2000</v>
@@ -5530,42 +5614,42 @@
         <v>9998881167</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>49</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K4" s="17">
         <v>1</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N4" s="17" t="s">
         <v>41</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C5" s="17">
         <v>22</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E5" s="17">
         <v>2000</v>
@@ -5574,16 +5658,16 @@
         <v>9998888995</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N5" s="17" t="s">
         <v>97</v>
@@ -5594,7 +5678,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="J13" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5610,29 +5694,29 @@
   <cols>
     <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="16" customFormat="1" ht="15.6">
       <c r="A1" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5640,16 +5724,16 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E2">
         <v>9888441127</v>
       </c>
       <c r="F2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5657,16 +5741,16 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E3">
         <v>9888441101</v>
       </c>
       <c r="F3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5674,16 +5758,16 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E4">
         <v>9888441111</v>
       </c>
       <c r="F4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5691,16 +5775,16 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E5">
         <v>9888441112</v>
       </c>
       <c r="F5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5708,10 +5792,10 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
         <v>100</v>
@@ -5720,7 +5804,7 @@
         <v>9888441113</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5728,19 +5812,19 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E7">
         <v>9888441113</v>
       </c>
       <c r="F7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/src/test-data/data for sign-up chat.xlsx
+++ b/src/test-data/data for sign-up chat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Gyansetu\G_TestCase001\src\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC135475-5B51-4F1A-B9F2-E51986E94DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576083D5-5EE5-4F51-A611-B65544C911C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SchoolUser_Registration" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="262">
   <si>
     <t>Email ID</t>
   </si>
@@ -807,9 +807,6 @@
     <t>walnutyy55@yopmail.com</t>
   </si>
   <si>
-    <t>himha66@yopmail.com</t>
-  </si>
-  <si>
     <t>Manimal HSS</t>
   </si>
   <si>
@@ -819,10 +816,16 @@
     <t>Sanju Vava</t>
   </si>
   <si>
-    <t>Rep N</t>
-  </si>
-  <si>
     <t>Studying</t>
+  </si>
+  <si>
+    <t>samjo66@yopmail.com</t>
+  </si>
+  <si>
+    <t>Samjo N</t>
+  </si>
+  <si>
+    <t>samjo668@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3FCDD0-35E5-40DE-9EAB-7DC01EE1849E}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.44140625" bestFit="1" customWidth="1"/>
@@ -1971,10 +1974,10 @@
     </row>
     <row r="2" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A2" s="22" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B2" s="23">
-        <v>8886663019</v>
+        <v>8886663022</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>3</v>
@@ -1982,10 +1985,10 @@
     </row>
     <row r="3" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A3" s="22" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B3" s="23">
-        <v>8886663018</v>
+        <v>8886663020</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>3</v>
@@ -1993,10 +1996,10 @@
     </row>
     <row r="4" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A4" s="22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B4" s="23">
-        <v>8886663017</v>
+        <v>8886663018</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>3</v>
@@ -2004,10 +2007,10 @@
     </row>
     <row r="5" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A5" s="22" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B5" s="23">
-        <v>8886663015</v>
+        <v>8886663017</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>3</v>
@@ -2015,10 +2018,10 @@
     </row>
     <row r="6" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A6" s="22" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B6" s="23">
-        <v>8886663010</v>
+        <v>8886663015</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>3</v>
@@ -2026,10 +2029,10 @@
     </row>
     <row r="7" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A7" s="22" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B7" s="23">
-        <v>8886663009</v>
+        <v>8886663010</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>3</v>
@@ -2037,10 +2040,10 @@
     </row>
     <row r="8" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A8" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B8" s="23">
-        <v>8886663008</v>
+        <v>8886663009</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>3</v>
@@ -2048,10 +2051,10 @@
     </row>
     <row r="9" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A9" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B9" s="23">
-        <v>8886663007</v>
+        <v>8886663008</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>3</v>
@@ -2059,19 +2062,25 @@
     </row>
     <row r="10" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A10" s="22" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B10" s="23">
-        <v>8886663006</v>
+        <v>8886663007</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="19" customFormat="1" ht="15.6">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="23">
+        <v>8886663006</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:3" s="19" customFormat="1" ht="15.6">
       <c r="A12" s="22"/>
@@ -2178,8 +2187,8 @@
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
     </row>
-    <row r="33" spans="1:3" ht="15.6">
-      <c r="A33" s="23"/>
+    <row r="33" spans="1:3" s="19" customFormat="1" ht="15.6">
+      <c r="A33" s="22"/>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
     </row>
@@ -2222,6 +2231,11 @@
       <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
+    </row>
+    <row r="42" spans="1:3" ht="15.6">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2354,7 +2368,7 @@
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" ht="28.8">
       <c r="A2" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B2" s="12">
         <v>26</v>
@@ -2387,7 +2401,7 @@
         <v>35</v>
       </c>
       <c r="L2" s="29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>13</v>
@@ -2396,7 +2410,7 @@
         <v>123</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>118</v>
@@ -2405,7 +2419,7 @@
         <v>9876655555</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S2" s="12" t="s">
         <v>41</v>
@@ -2414,13 +2428,13 @@
         <v>55</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>243</v>
       </c>
       <c r="W2" s="2">
-        <v>8876655466</v>
+        <v>8876655400</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>42</v>
